--- a/output/退職規程_いいかいご.xlsx
+++ b/output/退職規程_いいかいご.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -657,59 +657,65 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>（退職の申出）</t>
+          <t>（定年）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>第5条　従業員が自己都合により退職を希望する場合は、原則として退職希望日の30日前までに所定の退職届を提出しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="8" customHeight="1"/>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>（引継ぎ義務）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>第6条　退職する従業員は、会社が指定する業務の引継ぎを誠実に行い、職務上の責任を果たさなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="8" customHeight="1"/>
+          <t>第4条の2　従業員の定年は満60歳とし、満60歳に達した日の属する月の末日をもって退職とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2　定年に達した従業員が希望する場合は、高年齢者雇用安定法に基づき、満65歳まで継続雇用する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>（退職の申出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>第5条　従業員が自己都合により退職を希望する場合は、円滑な引継ぎのため、原則として退職希望日の30日前までに所定の退職届を提出するよう努めなければならない。</t>
+        </is>
+      </c>
+    </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>（会社物品の返還）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>第7条　退職する従業員は、退職日までに会社から貸与された備品、制服、身分証、書類、電子機器その他の物品を返還しなければならない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="8" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>（退職証明書の交付）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="32" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2　前項にかかわらず、退職の効力は民法の定めによる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>（解雇予告）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>第5条の2　会社が従業員を解雇する場合は、少なくとも30日前に予告するか、30日分以上の平均賃金（解雇予告手当）を支払う。ただし、労働基準監督署長の認定を受けた場合はこの限りでない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>第8条　従業員が退職した場合、本人の請求に基づき、労働基準法第22条に定める退職証明書を交付する。</t>
+          <t>2　予告の日数は、平均賃金を支払った日数分短縮することができる。</t>
         </is>
       </c>
     </row>
@@ -717,14 +723,14 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>（賃金の精算）</t>
+          <t>（引継ぎ義務）</t>
         </is>
       </c>
     </row>
     <row r="60" ht="32" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>第9条　退職に際しては、労働基準法第23条に基づき、未払賃金その他の金銭を退職日から7日以内に支払う。</t>
+          <t>第6条　退職する従業員は、会社が指定する業務の引継ぎを誠実に行い、職務上の責任を果たさなければならない。</t>
         </is>
       </c>
     </row>
@@ -732,44 +738,44 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>（秘密保持義務）</t>
+          <t>（会社物品の返還）</t>
         </is>
       </c>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>第10条　退職した従業員は、在職中に知り得た会社の営業秘密、顧客情報、個人情報その他の秘密を退職後も漏洩してはならない。</t>
+          <t>第7条　退職する従業員は、退職日までに会社から貸与された備品、制服、身分証、書類、電子機器その他の物品を返還しなければならない。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="8" customHeight="1"/>
-    <row r="65" ht="8" customHeight="1">
-      <c r="A65" s="7" t="inlineStr"/>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="n"/>
-    </row>
-    <row r="66" ht="10" customHeight="1"/>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>第3章　退職金</t>
-        </is>
-      </c>
-    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>（退職証明書の交付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>第8条　従業員が退職した場合、本人の請求に基づき、労働基準法第22条に定める退職証明書を交付する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="8" customHeight="1"/>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>（支給対象者）</t>
+          <t>（賃金の精算）</t>
         </is>
       </c>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>第11条　勤続1年以上の従業員が退職した場合、会社は退職金を支給する。ただし、第15条に定める不支給事由に該当する場合は支給しない。</t>
+          <t>第9条　退職に際しては、労働基準法第23条に基づき、本人（死亡の場合は遺族）の請求があったときから7日以内に、未払賃金その他の金銭を支払う。</t>
         </is>
       </c>
     </row>
@@ -777,341 +783,393 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>（勤続年数の算定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
+          <t>（秘密保持義務）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>第12条　勤続年数は、入社日から退職日までの期間により算定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>2　1年未満の端数については次のとおりとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1　6か月未満の端数は切り捨てる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　2　6か月以上の端数は1年に切り上げる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="8" customHeight="1"/>
+          <t>第10条　退職した従業員は、在職中に知り得た会社の営業秘密、顧客情報、個人情報その他の秘密を退職後も漏洩してはならない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="8" customHeight="1">
+      <c r="A74" s="7" t="inlineStr"/>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="8" t="n"/>
+    </row>
+    <row r="75" ht="10" customHeight="1"/>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>第3章　退職金</t>
+        </is>
+      </c>
+    </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>（退職金の算定方法）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
+          <t>（支給対象者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>第13条　退職金の額は、次の算式により算定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>退職金 ＝ 退職時基本給 × 支給係数 × 勤続年数</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="8" customHeight="1"/>
+          <t>第11条　勤続1年以上の従業員が退職した場合、会社は退職金を支給する。ただし、第15条に定める不支給事由に該当する場合は支給しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="8" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>（勤続年数の算定）</t>
+        </is>
+      </c>
+    </row>
     <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>（支給係数）</t>
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>第12条　勤続年数は、入社日から退職日までの期間により算定する。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
+          <t>2　1年未満の端数については次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1　6か月未満の端数は切り捨てる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2　6か月以上の端数は1年に切り上げる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="8" customHeight="1"/>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>（退職金の算定方法）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>第13条　退職金の額は、次の算式により算定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>退職金 ＝ 退職時基本給 × 支給係数 × 勤続年数</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>（支給係数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
           <t>第14条　支給係数は、勤続年数及び退職理由に応じて次のとおりとする。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="9" t="inlineStr">
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>勤続年数</t>
         </is>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>自己都合</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="C92" s="10" t="inlineStr">
         <is>
           <t>会社都合</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t>1年以上3年未満</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C93" s="12" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>3年以上6年未満</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="C94" s="12" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t>6年以上9年未満</t>
         </is>
       </c>
-      <c r="B86" s="12" t="inlineStr">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="C86" s="12" t="inlineStr">
+      <c r="C95" s="12" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>9年以上15年未満</t>
         </is>
       </c>
-      <c r="B87" s="12" t="inlineStr">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="C87" s="12" t="inlineStr">
+      <c r="C96" s="12" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>15年以上25年未満</t>
         </is>
       </c>
-      <c r="B88" s="12" t="inlineStr">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C97" s="12" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
         <is>
           <t>25年以上</t>
         </is>
       </c>
-      <c r="B89" s="12" t="inlineStr">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="C89" s="12" t="inlineStr">
+      <c r="C98" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="8" customHeight="1"/>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="99" ht="8" customHeight="1"/>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>（不支給事由）</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>第15条　従業員が次の各号のいずれかに該当する場合は、退職金を支給しない。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>1　懲戒解雇された場合</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>2　重大な背信行為により会社に著しい損害を与えた場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>3　虚偽の申告により雇用契約を締結したことが判明した場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>（支給手続）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>第16条　退職金は、退職日から2か月以内に本人の指定口座に振り込む。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>2　会社は必要に応じて退職金の一部または全部を分割して支給することができる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="8" customHeight="1"/>
-    <row r="101" ht="8" customHeight="1">
-      <c r="A101" s="7" t="inlineStr"/>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="8" t="n"/>
-    </row>
-    <row r="102" ht="10" customHeight="1"/>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>附則</t>
         </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
+          <t>3　虚偽の申告により雇用契約を締結したことが判明した場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="8" customHeight="1"/>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>（支給手続）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>第16条　退職金は、退職日から2か月以内に本人の指定口座に振り込む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>2　会社は、本人の同意を得た場合に限り、退職金を分割して支給することができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="8" customHeight="1"/>
+    <row r="110" ht="8" customHeight="1">
+      <c r="A110" s="7" t="inlineStr"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="8" t="n"/>
+    </row>
+    <row r="111" ht="10" customHeight="1"/>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>附則</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
           <t>1　本規程に定めのない事項は、就業規則その他関係規程による。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>2　本規程は令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="64">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A114:E114"/>
     <mergeCell ref="A82:E82"/>
     <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A98:E98"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A107:E107"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
-    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A110:E110"/>
     <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A54:E54"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A108:E108"/>
     <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A95:E95"/>
     <mergeCell ref="A101:E101"/>
+    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A104:E104"/>
+    <mergeCell ref="A113:E113"/>
     <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A106:E106"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A91:E91"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A100:E100"/>
     <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A112:E112"/>
     <mergeCell ref="A68:E68"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A102:E102"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
